--- a/data/source-workbooks/main-source_enhanced_bof_aligned.xlsx
+++ b/data/source-workbooks/main-source_enhanced_bof_aligned.xlsx
@@ -1813,12 +1813,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="F2" s="63" t="n">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="F3" s="63" t="n">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="F4" s="63" t="n">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="F5" s="63" t="n">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="F6" s="63" t="n">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="F7" s="63" t="n">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="F8" s="63" t="n">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="F9" s="63" t="n">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="F10" s="63" t="n">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="F11" s="63" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="F12" s="63" t="n">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH 44308</t>
+          <t>1040 Demo Street, Akron, OH 44308</t>
         </is>
       </c>
       <c r="F13" s="63" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7942,12 +7942,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8460,12 +8460,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8978,12 +8978,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -21738,12 +21738,12 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH 44113</t>
+          <t>220 Demo Street, Cleveland, OH 44113</t>
         </is>
       </c>
       <c r="E6" s="32">
@@ -21798,12 +21798,12 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL 60611</t>
+          <t>770 Demo Street, Chicago, IL 60611</t>
         </is>
       </c>
       <c r="E7" s="32">
@@ -21852,12 +21852,12 @@
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA 30308</t>
+          <t>960 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="E8" s="32">
@@ -21906,12 +21906,12 @@
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH 44114</t>
+          <t>520 Demo Street, Cleveland, OH 44114</t>
         </is>
       </c>
       <c r="E9" s="32">
@@ -21960,12 +21960,12 @@
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH 43215</t>
+          <t>150 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="E10" s="32">
@@ -22014,12 +22014,12 @@
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX 75202</t>
+          <t>810 Demo Street, Dallas, TX 75202</t>
         </is>
       </c>
       <c r="E11" s="32">
@@ -22068,12 +22068,12 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH 44115</t>
+          <t>1020 Demo Street, Cleveland, OH 44115</t>
         </is>
       </c>
       <c r="E12" s="32">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH 43604</t>
+          <t>530 Demo Street, Toledo, OH 43604</t>
         </is>
       </c>
       <c r="E13" s="32">
@@ -22176,12 +22176,12 @@
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH 43215</t>
+          <t>630 Demo Street, Columbus, OH 43215</t>
         </is>
       </c>
       <c r="E14" s="32">
@@ -22230,12 +22230,12 @@
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL 60603</t>
+          <t>130 Demo Street, Chicago, IL 60603</t>
         </is>
       </c>
       <c r="E15" s="32">
@@ -22284,12 +22284,12 @@
       </c>
       <c r="C16" s="32" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA 30308</t>
+          <t>900 Demo Street, Atlanta, GA 30308</t>
         </is>
       </c>
       <c r="E16" s="32">
@@ -33206,12 +33206,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -33246,12 +33246,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -33286,12 +33286,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -33326,12 +33326,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -33406,12 +33406,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -33446,12 +33446,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>206-667-3424</t>
+          <t>206-555-0102</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1240 W 6th St, Cleveland, OH</t>
+          <t>220 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -33486,12 +33486,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -33526,12 +33526,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -33566,12 +33566,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -33606,12 +33606,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -33646,12 +33646,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -33686,12 +33686,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -33726,12 +33726,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>707-773-6386</t>
+          <t>707-555-0100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>450 N Michigan Ave, Chicago, IL</t>
+          <t>770 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -33766,12 +33766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -33806,12 +33806,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -33846,12 +33846,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -33886,12 +33886,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -33926,12 +33926,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -33966,12 +33966,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -34006,12 +34006,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>675-486-1335</t>
+          <t>675-555-0100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>780 Peachtree St, Atlanta, GA</t>
+          <t>960 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -34046,12 +34046,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -34086,12 +34086,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -34126,12 +34126,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -34166,12 +34166,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -34206,12 +34206,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -34246,12 +34246,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -34286,12 +34286,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>359-469-5960</t>
+          <t>359-555-0100</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2200 Superior Ave, Cleveland, OH</t>
+          <t>520 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -34326,12 +34326,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -34366,12 +34366,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -34406,12 +34406,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -34446,12 +34446,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -34486,12 +34486,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -34526,12 +34526,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -34566,12 +34566,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>871-429-6220</t>
+          <t>871-555-0100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>115 E Broad St, Columbus, OH</t>
+          <t>150 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -34606,12 +34606,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -34646,12 +34646,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -34686,12 +34686,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -34726,12 +34726,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -34766,12 +34766,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -34806,12 +34806,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -34846,12 +34846,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>283-876-4322</t>
+          <t>283-555-0100</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>500 Pacific Ave, Dallas, TX</t>
+          <t>810 Demo Street, Dallas, TX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -34886,12 +34886,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -34926,12 +34926,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -34966,12 +34966,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -35006,12 +35006,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -35046,12 +35046,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -35126,12 +35126,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>896-828-7164</t>
+          <t>896-555-0100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>815 Prospect Ave, Cleveland, OH</t>
+          <t>1020 Demo Street, Cleveland, OH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -35166,12 +35166,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -35206,12 +35206,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -35246,12 +35246,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -35286,12 +35286,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -35326,12 +35326,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -35366,12 +35366,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -35406,12 +35406,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>820-223-4829</t>
+          <t>820-555-0100</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>240 Madison Ave, Toledo, OH</t>
+          <t>530 Demo Street, Toledo, OH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -35446,12 +35446,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -35486,12 +35486,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -35526,12 +35526,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -35566,12 +35566,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -35606,12 +35606,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -35646,12 +35646,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -35686,12 +35686,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>206-700-7666</t>
+          <t>206-555-0103</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>330 Civic Center Dr, Columbus, OH</t>
+          <t>630 Demo Street, Columbus, OH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -35726,12 +35726,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -35766,12 +35766,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -35806,12 +35806,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -35846,12 +35846,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -35886,12 +35886,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -35926,12 +35926,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -35966,12 +35966,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>582-987-2387</t>
+          <t>582-555-0100</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>110 W Adams St, Chicago, IL</t>
+          <t>130 Demo Street, Chicago, IL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -36006,12 +36006,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -36046,12 +36046,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -36086,12 +36086,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -36126,12 +36126,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -36166,12 +36166,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -36206,12 +36206,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -36246,12 +36246,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>337-857-3607</t>
+          <t>337-555-0100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>600 Peachtree St, Atlanta, GA</t>
+          <t>900 Demo Street, Atlanta, GA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -36286,12 +36286,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -36326,12 +36326,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -36366,12 +36366,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -36406,12 +36406,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -36446,12 +36446,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -36486,12 +36486,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -36526,12 +36526,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>618-623-9317</t>
+          <t>618-555-0100</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>88 S Main St, Akron, OH</t>
+          <t>1040 Demo Street, Akron, OH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
